--- a/data/proyectos_ds19.xlsx
+++ b/data/proyectos_ds19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7bd4bafa3350f995/04. Trabajos/0. Equidad Urbana Consultora/0. EU RESPALDO 2020-2025/03.  Estudios/equidad-comunidades/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_068D3BC2F4C07C984EAE7020B6E72AD5FF7F1ECE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44952306-69F2-4769-8C78-084C140D2928}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_03197BCB3D20BD4E62826858CDC3455C357C8848" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FB313C7-7131-4C44-835F-E1267AAFAD27}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="70">
   <si>
     <t>Actualización de Proyectos DS19</t>
   </si>
@@ -30,9 +30,6 @@
     <t>1. Agrega todos los proyectos vigentes en la hoja Proyectos, con su comuna y correo de contacto. Se muestran por defecto.</t>
   </si>
   <si>
-    <t>3. Escribe la actividad como quieres que aparezca en la web, por ejemplo: Taller de organización comunitaria.</t>
-  </si>
-  <si>
     <t>4. Usa Visible = No solo si deseas ocultar una actividad o proyecto de la web.</t>
   </si>
   <si>
@@ -51,12 +48,60 @@
     <t>Comuna</t>
   </si>
   <si>
+    <t>Próxima actividad</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Horario</t>
+  </si>
+  <si>
+    <t>Lugar</t>
+  </si>
+  <si>
+    <t>Visible</t>
+  </si>
+  <si>
+    <t>Gran Avenida</t>
+  </si>
+  <si>
+    <t>El Bosque</t>
+  </si>
+  <si>
+    <t>15:00 y 16:30 horas</t>
+  </si>
+  <si>
+    <t>Gran Avenida XXX</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Valles de Rengo III Etapa 1</t>
+  </si>
+  <si>
+    <t>Rengo</t>
+  </si>
+  <si>
+    <t>Pataguas XI</t>
+  </si>
+  <si>
+    <t>Lampa</t>
+  </si>
+  <si>
+    <t>Principal 1385</t>
+  </si>
+  <si>
+    <t>Conchalí</t>
+  </si>
+  <si>
+    <t>18:00 horas</t>
+  </si>
+  <si>
     <t>Correo de contacto</t>
   </si>
   <si>
-    <t>Visible</t>
-  </si>
-  <si>
     <t>Pie Andino I</t>
   </si>
   <si>
@@ -81,12 +126,6 @@
     <t>barriojardinesdebuin.pis@gmail.com</t>
   </si>
   <si>
-    <t>Valles de Rengo III Etapa 1</t>
-  </si>
-  <si>
-    <t>Rengo</t>
-  </si>
-  <si>
     <t>vallesderengo3.pis@gmail.com</t>
   </si>
   <si>
@@ -108,16 +147,7 @@
     <t>jardinessb.pis@gmail.com</t>
   </si>
   <si>
-    <t>Pataguas XI</t>
-  </si>
-  <si>
-    <t>Lampa</t>
-  </si>
-  <si>
-    <t>Principal 1385</t>
-  </si>
-  <si>
-    <t>Conchalí</t>
+    <t>ds19rm@socovesa.cl</t>
   </si>
   <si>
     <t>principal1385@gmail.com</t>
@@ -150,9 +180,6 @@
     <t xml:space="preserve">Gran Avenida </t>
   </si>
   <si>
-    <t>El Bosque</t>
-  </si>
-  <si>
     <t>plands19@rvc.cl</t>
   </si>
   <si>
@@ -168,59 +195,50 @@
     <t>pisvallesderengo3.2@gmail.com</t>
   </si>
   <si>
-    <t>Próxima actividad</t>
-  </si>
-  <si>
-    <t>Fecha</t>
-  </si>
-  <si>
-    <t>Horario</t>
-  </si>
-  <si>
-    <t>Lugar</t>
-  </si>
-  <si>
-    <t>Gran Avenida</t>
-  </si>
-  <si>
-    <t>Repetición Visita a la obra</t>
-  </si>
-  <si>
-    <t>Sí</t>
-  </si>
-  <si>
-    <t>Repetición Taller de Organización Comunitaria</t>
+    <t>Opciones de actividad</t>
+  </si>
+  <si>
+    <t>Visita a la obra</t>
+  </si>
+  <si>
+    <t>Taller de Uso, Cuidado y Mantención</t>
+  </si>
+  <si>
+    <t>2. Completa Próxima actividad, Fecha, Horario y Lugar. El correo de contacto se mantiene en la hoja Proyectos.</t>
+  </si>
+  <si>
+    <t>Taller de Derechos y Deberes</t>
+  </si>
+  <si>
+    <t>3. Elige la Próxima actividad desde la lista desplegable. Para repeticiones, selecciona la opción correspondiente.</t>
+  </si>
+  <si>
+    <t>Taller de Redes</t>
   </si>
   <si>
     <t>Taller de Organización Comunitaria</t>
   </si>
   <si>
-    <t>Tres turnos:</t>
-  </si>
-  <si>
-    <t>Redes comunitarias</t>
-  </si>
-  <si>
-    <t>18:00 horas</t>
-  </si>
-  <si>
-    <t>3. Completa Próxima actividad, Fecha, Horario y Lugar. El correo de contacto se mantiene en la hoja Proyectos.</t>
-  </si>
-  <si>
-    <t>ds19rm@socovesa.cl</t>
-  </si>
-  <si>
-    <t>15:00 y 16:30 horas</t>
-  </si>
-  <si>
-    <t>Gran Avenida XXX</t>
+    <t>Repetición de la Visita a la obra</t>
+  </si>
+  <si>
+    <t>Repetición del Taller de Uso, Cuidado y Mantención</t>
+  </si>
+  <si>
+    <t>Repetición del Taller de Derechos y Deberes</t>
+  </si>
+  <si>
+    <t>Repetición del Taller de Redes</t>
+  </si>
+  <si>
+    <t>Repetición del Taller de Organización Comunitaria</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -247,8 +265,14 @@
       <color rgb="FF273B3A"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -273,6 +297,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF174F5A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196774"/>
       </patternFill>
     </fill>
   </fills>
@@ -440,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -501,6 +530,12 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -516,10 +551,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -716,54 +747,94 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF7BAF9B"/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="19.5">
+    <row r="1" spans="1:3" ht="19.5">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" ht="30.95" customHeight="1">
+      <c r="C1" s="23" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="C2" s="22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="30.95" customHeight="1">
       <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" ht="30.95" customHeight="1">
+      <c r="C3" s="22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30.95" customHeight="1">
       <c r="A4" s="12" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" ht="30.95" customHeight="1">
+      <c r="C4" s="22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="33.950000000000003" customHeight="1">
       <c r="A5" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="30.95" customHeight="1">
+      <c r="A6" s="12" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" ht="30.95" customHeight="1">
-      <c r="A6" s="12" t="s">
+      <c r="C6" s="22" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="30.95" customHeight="1">
+      <c r="A7" s="12" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" ht="30.95" customHeight="1">
-      <c r="A7" s="12" t="s">
+      <c r="C7" s="22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30.95" customHeight="1">
+      <c r="A8" s="12" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" ht="30.95" customHeight="1">
-      <c r="A8" s="12" t="s">
+      <c r="C8" s="22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="30.95" customHeight="1">
+      <c r="A9" s="12" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" ht="30.95" customHeight="1">
-      <c r="A9" s="12" t="s">
-        <v>6</v>
+      <c r="C9" s="22" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="C10" s="22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="28.5">
+      <c r="C11" s="22" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -772,7 +843,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF174F5A"/>
   </sheetPr>
@@ -790,111 +861,108 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="D1" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="G1" s="21" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D2" s="13">
         <v>46304</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="H2" s="15"/>
     </row>
     <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D3" s="13">
         <v>46310</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D4" s="13">
         <v>46312</v>
       </c>
-      <c r="E4" t="s">
-        <v>57</v>
-      </c>
       <c r="F4" s="3"/>
       <c r="G4" s="4" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D5" s="13">
         <v>46316</v>
       </c>
       <c r="E5" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="4" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="H5" s="4"/>
     </row>
@@ -1818,11 +1886,23 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="G2:G103 G2:H101" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="G2:G103 G2:H101" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0100-000001000000}">
+          <x14:formula1>
+            <xm:f>Instrucciones!$C$2:$C$11</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C500</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -1842,183 +1922,183 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>8</v>
-      </c>
       <c r="C1" s="17" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="14" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D2" s="15"/>
     </row>
     <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D3" s="4"/>
     </row>
     <row r="4" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="C5" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D5" s="4"/>
     </row>
     <row r="6" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="D8" s="4"/>
     </row>
     <row r="9" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D9" s="4"/>
     </row>
     <row r="10" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D10" s="4"/>
     </row>
     <row r="11" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D11" s="4"/>
     </row>
     <row r="12" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D13" s="4"/>
     </row>
     <row r="14" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D15" s="4"/>
     </row>

--- a/data/proyectos_ds19.xlsx
+++ b/data/proyectos_ds19.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7bd4bafa3350f995/04. Trabajos/0. Equidad Urbana Consultora/0. EU RESPALDO 2020-2025/03.  Estudios/equidad-comunidades/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_E7ED3FDEADE832884C851FCF54C87AF5188CC886" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{230BDF06-20B0-442A-9885-5A7F532A8022}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="11_E7ED3FDEADE832884C851FCF54C87AF5188CC886" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB6734E4-4B85-4370-89D1-FE388481E4AE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="75">
   <si>
     <t>Actualización de Proyectos DS19</t>
   </si>
@@ -63,15 +63,9 @@
     <t>Visible</t>
   </si>
   <si>
-    <t>Gran Avenida</t>
-  </si>
-  <si>
     <t>El Bosque</t>
   </si>
   <si>
-    <t>15:00 y 16:30 horas</t>
-  </si>
-  <si>
     <t>Sí</t>
   </si>
   <si>
@@ -234,23 +228,32 @@
     <t>Actividad de cierre del PIS</t>
   </si>
   <si>
-    <t>Gran Avenida #9680</t>
-  </si>
-  <si>
-    <t>Sede Junta de Vecinos Libertad (Guangualí Sur #159, Rengo)</t>
-  </si>
-  <si>
-    <t>9:00, 10:30 y 12:00 horas</t>
-  </si>
-  <si>
-    <t>Casino del Colegio Emprender (Los Halcones 1000, Lampa)</t>
+    <t>11:00 y 12:30 horas</t>
+  </si>
+  <si>
+    <t>Local comercial ubicado al interior del proyecto. Ingreso por calle Juan Egenau</t>
+  </si>
+  <si>
+    <t>16:00 horas</t>
+  </si>
+  <si>
+    <t>Centro Municipal Canelo de Nos Av. Diego Portales #3020 San Bernardo</t>
+  </si>
+  <si>
+    <t>Escuela Unesco de Conchalí ubicada en la calle Tronador N° 1695</t>
+  </si>
+  <si>
+    <t>Panorámico I - Torre A</t>
+  </si>
+  <si>
+    <t>Auditorio INACAP, ubicado en Av. Edmundo Pérez Zujovic N.º 11.092</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -289,6 +292,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF273B3A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -323,7 +341,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -516,11 +534,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF174F5A"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFE3ECEA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -590,20 +619,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -620,6 +652,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -832,12 +868,12 @@
         <v>0</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="C2" s="22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="30.95" customHeight="1">
@@ -845,23 +881,23 @@
         <v>1</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30.95" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="33.950000000000003" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30.95" customHeight="1">
@@ -869,7 +905,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30.95" customHeight="1">
@@ -877,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30.95" customHeight="1">
@@ -885,7 +921,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30.95" customHeight="1">
@@ -893,22 +929,22 @@
         <v>5</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="C10" s="22" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="28.5">
       <c r="C11" s="22" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="C12" s="22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -957,97 +993,99 @@
       </c>
       <c r="H1" s="20"/>
     </row>
-    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A2" s="24" t="s">
-        <v>13</v>
+    <row r="2" spans="1:8" ht="49.5" customHeight="1" thickBot="1">
+      <c r="A2" s="27" t="s">
+        <v>19</v>
       </c>
       <c r="B2" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="30">
+        <v>46324</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="25">
-        <v>46275</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="26" t="s">
+      <c r="H2" s="15"/>
+    </row>
+    <row r="3" spans="1:8" ht="40.5" customHeight="1" thickBot="1">
+      <c r="A3" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="30">
+        <v>46331</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" customHeight="1" thickBot="1">
+      <c r="A4" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="30">
+        <v>46337</v>
+      </c>
+      <c r="E4" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="G2" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="15"/>
-    </row>
-    <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A3" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" s="25">
-        <v>46310</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="27" t="s">
+      <c r="F4" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A4" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="25">
-        <v>46312</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" s="29" t="s">
+      <c r="G4" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" ht="33.75" customHeight="1" thickBot="1">
+      <c r="A5" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="G4" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A5" s="22" t="s">
+      <c r="B5" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="30">
+        <v>46345</v>
+      </c>
+      <c r="E5" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="25">
-        <v>46316</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="28"/>
-      <c r="G5" s="29" t="s">
-        <v>16</v>
+      <c r="F5" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>14</v>
       </c>
       <c r="H5" s="4"/>
     </row>
@@ -1970,8 +2008,9 @@
       <c r="G103" s="8"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="G6:G101 H2:H101 G6:G103" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="H2:H101 G6:G103" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1983,7 +2022,7 @@
           <x14:formula1>
             <xm:f>Instrucciones!$C$2:$C$12</xm:f>
           </x14:formula1>
-          <xm:sqref>C6:C500</xm:sqref>
+          <xm:sqref>C12:C500 C6:C7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2013,7 +2052,7 @@
         <v>7</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D1" s="18" t="s">
         <v>12</v>
@@ -2021,169 +2060,169 @@
     </row>
     <row r="2" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>25</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>27</v>
       </c>
       <c r="D2" s="15"/>
     </row>
     <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" s="4"/>
     </row>
     <row r="4" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5" s="4"/>
     </row>
     <row r="6" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D8" s="4"/>
     </row>
     <row r="9" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D9" s="4"/>
     </row>
     <row r="10" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D10" s="4"/>
     </row>
     <row r="11" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="D11" s="4"/>
     </row>
     <row r="12" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D13" s="4"/>
     </row>
     <row r="14" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" s="4"/>
     </row>
@@ -2710,5 +2749,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>